--- a/docs/dry-run/sheets/4-phase2-closed-final.xlsx
+++ b/docs/dry-run/sheets/4-phase2-closed-final.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="93">
   <si>
     <t>phase</t>
   </si>
@@ -73,7 +73,7 @@
     <t>Dan Mercer</t>
   </si>
   <si>
-    <t>7/12</t>
+    <t>11/10</t>
   </si>
   <si>
     <t>Hit</t>
@@ -164,9 +164,6 @@
   </si>
   <si>
     <t>Medalist - Round 1</t>
-  </si>
-  <si>
-    <t>11/10</t>
   </si>
   <si>
     <t>6/1</t>
@@ -749,16 +746,16 @@
         <v>19</v>
       </c>
       <c r="I2">
-        <v>-140</v>
+        <v>110</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2">
-        <v>0.5833333333333334</v>
+        <v>0.47619047619047616</v>
       </c>
       <c r="L2">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M2" t="s">
         <v>21</v>
@@ -799,7 +796,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="L3">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M3" t="s">
         <v>24</v>
@@ -840,7 +837,7 @@
         <v>0.2</v>
       </c>
       <c r="L4">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M4" t="s">
         <v>24</v>
@@ -881,7 +878,7 @@
         <v>0.1</v>
       </c>
       <c r="L5">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M5" t="s">
         <v>24</v>
@@ -922,7 +919,7 @@
         <v>0.125</v>
       </c>
       <c r="L6">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M6" t="s">
         <v>24</v>
@@ -963,7 +960,7 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="L7">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M7" t="s">
         <v>24</v>
@@ -1004,7 +1001,7 @@
         <v>0.0625</v>
       </c>
       <c r="L8">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M8" t="s">
         <v>24</v>
@@ -1045,7 +1042,7 @@
         <v>0.0625</v>
       </c>
       <c r="L9">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M9" t="s">
         <v>24</v>
@@ -1086,7 +1083,7 @@
         <v>0.0625</v>
       </c>
       <c r="L10">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M10" t="s">
         <v>24</v>
@@ -1127,7 +1124,7 @@
         <v>0.0196078431372549</v>
       </c>
       <c r="L11">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M11" t="s">
         <v>24</v>
@@ -1168,7 +1165,7 @@
         <v>0.0196078431372549</v>
       </c>
       <c r="L12">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M12" t="s">
         <v>24</v>
@@ -1209,7 +1206,7 @@
         <v>0.009900990099009901</v>
       </c>
       <c r="L13">
-        <v>1.6552064199632632</v>
+        <v>1.548063562820406</v>
       </c>
       <c r="M13" t="s">
         <v>24</v>
@@ -1654,7 +1651,7 @@
         <v>110</v>
       </c>
       <c r="J24" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="K24">
         <v>0.47619047619047616</v>
@@ -1777,7 +1774,7 @@
         <v>600</v>
       </c>
       <c r="J27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K27">
         <v>0.14285714285714285</v>
@@ -1818,7 +1815,7 @@
         <v>600</v>
       </c>
       <c r="J28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K28">
         <v>0.14285714285714285</v>
@@ -2128,7 +2125,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E36">
         <v>4</v>
@@ -2137,7 +2134,7 @@
         <v>35</v>
       </c>
       <c r="G36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H36" t="s">
         <v>19</v>
@@ -2146,7 +2143,7 @@
         <v>-130</v>
       </c>
       <c r="J36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K36">
         <v>0.5652173913043478</v>
@@ -2169,7 +2166,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E37">
         <v>4</v>
@@ -2178,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="G37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
@@ -2187,7 +2184,7 @@
         <v>130</v>
       </c>
       <c r="J37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K37">
         <v>0.43478260869565216</v>
@@ -2210,7 +2207,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E38">
         <v>5</v>
@@ -2219,7 +2216,7 @@
         <v>37</v>
       </c>
       <c r="G38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H38" t="s">
         <v>25</v>
@@ -2251,7 +2248,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E39">
         <v>5</v>
@@ -2260,7 +2257,7 @@
         <v>38</v>
       </c>
       <c r="G39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H39" t="s">
         <v>27</v>
@@ -2269,7 +2266,7 @@
         <v>250</v>
       </c>
       <c r="J39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K39">
         <v>0.2857142857142857</v>
@@ -2292,7 +2289,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E40">
         <v>5</v>
@@ -2301,7 +2298,7 @@
         <v>39</v>
       </c>
       <c r="G40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H40" t="s">
         <v>29</v>
@@ -2333,7 +2330,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E41">
         <v>5</v>
@@ -2342,7 +2339,7 @@
         <v>40</v>
       </c>
       <c r="G41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H41" t="s">
         <v>31</v>
@@ -2374,7 +2371,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -2383,7 +2380,7 @@
         <v>41</v>
       </c>
       <c r="G42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H42" t="s">
         <v>35</v>
@@ -2401,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="M42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -2415,7 +2412,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E43">
         <v>6</v>
@@ -2424,7 +2421,7 @@
         <v>42</v>
       </c>
       <c r="G43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H43" t="s">
         <v>36</v>
@@ -2442,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -2456,7 +2453,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44">
         <v>7</v>
@@ -2465,10 +2462,10 @@
         <v>43</v>
       </c>
       <c r="G44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I44">
         <v>150</v>
@@ -2497,7 +2494,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E45">
         <v>7</v>
@@ -2506,10 +2503,10 @@
         <v>44</v>
       </c>
       <c r="G45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I45">
         <v>150</v>
@@ -2538,7 +2535,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E46">
         <v>7</v>
@@ -2547,10 +2544,10 @@
         <v>45</v>
       </c>
       <c r="G46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I46">
         <v>150</v>
@@ -2579,7 +2576,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E47">
         <v>8</v>
@@ -2588,10 +2585,10 @@
         <v>46</v>
       </c>
       <c r="G47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I47">
         <v>100</v>
@@ -2606,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -2620,7 +2617,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E48">
         <v>8</v>
@@ -2629,10 +2626,10 @@
         <v>47</v>
       </c>
       <c r="G48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I48">
         <v>100</v>
@@ -2647,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="M48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -2661,7 +2658,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E49">
         <v>9</v>
@@ -2670,10 +2667,10 @@
         <v>48</v>
       </c>
       <c r="G49" t="s">
+        <v>67</v>
+      </c>
+      <c r="H49" t="s">
         <v>68</v>
-      </c>
-      <c r="H49" t="s">
-        <v>69</v>
       </c>
       <c r="I49">
         <v>200</v>
@@ -2702,7 +2699,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E50">
         <v>9</v>
@@ -2711,16 +2708,16 @@
         <v>49</v>
       </c>
       <c r="G50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I50">
         <v>-200</v>
       </c>
       <c r="J50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K50">
         <v>0.6666666666666666</v>
@@ -2743,7 +2740,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E51">
         <v>10</v>
@@ -2752,10 +2749,10 @@
         <v>50</v>
       </c>
       <c r="G51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I51">
         <v>150</v>
@@ -2784,7 +2781,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E52">
         <v>10</v>
@@ -2793,16 +2790,16 @@
         <v>51</v>
       </c>
       <c r="G52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I52">
         <v>-150</v>
       </c>
       <c r="J52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K52">
         <v>0.6</v>
@@ -2825,7 +2822,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E53">
         <v>11</v>
@@ -2834,16 +2831,16 @@
         <v>52</v>
       </c>
       <c r="G53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I53">
         <v>-130</v>
       </c>
       <c r="J53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K53">
         <v>0.5652173913043478</v>
@@ -2852,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -2866,7 +2863,7 @@
         <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E54">
         <v>11</v>
@@ -2875,16 +2872,16 @@
         <v>53</v>
       </c>
       <c r="G54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I54">
         <v>130</v>
       </c>
       <c r="J54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K54">
         <v>0.43478260869565216</v>
@@ -2893,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="M54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
@@ -2907,7 +2904,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E55">
         <v>12</v>
@@ -2916,16 +2913,16 @@
         <v>54</v>
       </c>
       <c r="G55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I55">
         <v>-110</v>
       </c>
       <c r="J55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K55">
         <v>0.5238095238095238</v>
@@ -2948,7 +2945,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E56">
         <v>12</v>
@@ -2957,16 +2954,16 @@
         <v>55</v>
       </c>
       <c r="G56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I56">
         <v>110</v>
       </c>
       <c r="J56" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="K56">
         <v>0.47619047619047616</v>
@@ -2989,7 +2986,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E57">
         <v>13</v>
@@ -2998,16 +2995,16 @@
         <v>56</v>
       </c>
       <c r="G57" t="s">
+        <v>76</v>
+      </c>
+      <c r="H57" t="s">
         <v>77</v>
-      </c>
-      <c r="H57" t="s">
-        <v>78</v>
       </c>
       <c r="I57">
         <v>-120</v>
       </c>
       <c r="J57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K57">
         <v>0.5454545454545454</v>
@@ -3030,7 +3027,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E58">
         <v>13</v>
@@ -3039,16 +3036,16 @@
         <v>57</v>
       </c>
       <c r="G58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I58">
         <v>120</v>
       </c>
       <c r="J58" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K58">
         <v>0.45454545454545453</v>
@@ -3130,7 +3127,7 @@
         <v>250</v>
       </c>
       <c r="J60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K60">
         <v>0.2857142857142857</v>
@@ -3212,7 +3209,7 @@
         <v>1000</v>
       </c>
       <c r="J62" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K62">
         <v>0.09090909090909091</v>
@@ -3253,7 +3250,7 @@
         <v>2000</v>
       </c>
       <c r="J63" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K63">
         <v>0.047619047619047616</v>
@@ -3285,7 +3282,7 @@
         <v>63</v>
       </c>
       <c r="G64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s">
         <v>36</v>
@@ -3294,7 +3291,7 @@
         <v>120</v>
       </c>
       <c r="J64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K64">
         <v>0.45454545454545453</v>
@@ -3326,7 +3323,7 @@
         <v>64</v>
       </c>
       <c r="G65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s">
         <v>27</v>
@@ -3335,7 +3332,7 @@
         <v>120</v>
       </c>
       <c r="J65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K65">
         <v>0.45454545454545453</v>
@@ -3367,7 +3364,7 @@
         <v>65</v>
       </c>
       <c r="G66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s">
         <v>33</v>
@@ -3376,7 +3373,7 @@
         <v>120</v>
       </c>
       <c r="J66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K66">
         <v>0.45454545454545453</v>
@@ -3408,10 +3405,10 @@
         <v>66</v>
       </c>
       <c r="G67" t="s">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s">
         <v>84</v>
-      </c>
-      <c r="H67" t="s">
-        <v>85</v>
       </c>
       <c r="I67">
         <v>5000</v>
@@ -3449,7 +3446,7 @@
         <v>67</v>
       </c>
       <c r="G68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s">
         <v>31</v>
@@ -3458,7 +3455,7 @@
         <v>120</v>
       </c>
       <c r="J68" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K68">
         <v>0.45454545454545453</v>
@@ -3490,7 +3487,7 @@
         <v>68</v>
       </c>
       <c r="G69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s">
         <v>35</v>
@@ -3499,7 +3496,7 @@
         <v>120</v>
       </c>
       <c r="J69" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K69">
         <v>0.45454545454545453</v>
@@ -3531,7 +3528,7 @@
         <v>69</v>
       </c>
       <c r="G70" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H70" t="s">
         <v>40</v>
@@ -3560,7 +3557,7 @@
         <v>15</v>
       </c>
       <c r="C71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D71" t="s">
         <v>17</v>
@@ -3572,7 +3569,7 @@
         <v>70</v>
       </c>
       <c r="G71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H71" t="s">
         <v>19</v>
@@ -3581,7 +3578,7 @@
         <v>110</v>
       </c>
       <c r="J71" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="K71">
         <v>0.47619047619047616</v>
@@ -3601,7 +3598,7 @@
         <v>15</v>
       </c>
       <c r="C72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D72" t="s">
         <v>17</v>
@@ -3613,7 +3610,7 @@
         <v>71</v>
       </c>
       <c r="G72" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H72" t="s">
         <v>22</v>
@@ -3622,7 +3619,7 @@
         <v>120</v>
       </c>
       <c r="J72" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K72">
         <v>0.45454545454545453</v>
@@ -3642,7 +3639,7 @@
         <v>15</v>
       </c>
       <c r="C73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D73" t="s">
         <v>17</v>
@@ -3654,7 +3651,7 @@
         <v>72</v>
       </c>
       <c r="G73" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s">
         <v>25</v>
@@ -3663,7 +3660,7 @@
         <v>220</v>
       </c>
       <c r="J73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K73">
         <v>0.3125</v>
@@ -3683,7 +3680,7 @@
         <v>15</v>
       </c>
       <c r="C74" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D74" t="s">
         <v>17</v>
@@ -3695,7 +3692,7 @@
         <v>73</v>
       </c>
       <c r="G74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H74" t="s">
         <v>27</v>
@@ -3704,7 +3701,7 @@
         <v>1000</v>
       </c>
       <c r="J74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K74">
         <v>0.09090909090909091</v>
@@ -3724,7 +3721,7 @@
         <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D75" t="s">
         <v>17</v>
@@ -3736,7 +3733,7 @@
         <v>74</v>
       </c>
       <c r="G75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H75" t="s">
         <v>29</v>
@@ -3765,7 +3762,7 @@
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D76" t="s">
         <v>17</v>
@@ -3777,7 +3774,7 @@
         <v>75</v>
       </c>
       <c r="G76" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H76" t="s">
         <v>31</v>
@@ -3806,7 +3803,7 @@
         <v>15</v>
       </c>
       <c r="C77" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D77" t="s">
         <v>17</v>
@@ -3818,7 +3815,7 @@
         <v>76</v>
       </c>
       <c r="G77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H77" t="s">
         <v>33</v>
@@ -3847,7 +3844,7 @@
         <v>15</v>
       </c>
       <c r="C78" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D78" t="s">
         <v>17</v>
@@ -3859,7 +3856,7 @@
         <v>77</v>
       </c>
       <c r="G78" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s">
         <v>35</v>
@@ -3888,7 +3885,7 @@
         <v>15</v>
       </c>
       <c r="C79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D79" t="s">
         <v>17</v>
@@ -3900,7 +3897,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H79" t="s">
         <v>36</v>
@@ -3929,7 +3926,7 @@
         <v>15</v>
       </c>
       <c r="C80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D80" t="s">
         <v>17</v>
@@ -3941,7 +3938,7 @@
         <v>79</v>
       </c>
       <c r="G80" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H80" t="s">
         <v>37</v>
@@ -3970,7 +3967,7 @@
         <v>15</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81" t="s">
         <v>17</v>
@@ -3982,7 +3979,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H81" t="s">
         <v>39</v>
@@ -4011,7 +4008,7 @@
         <v>15</v>
       </c>
       <c r="C82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D82" t="s">
         <v>17</v>
@@ -4023,7 +4020,7 @@
         <v>81</v>
       </c>
       <c r="G82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H82" t="s">
         <v>40</v>
@@ -4052,10 +4049,10 @@
         <v>15</v>
       </c>
       <c r="C83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D83" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E83">
         <v>17</v>
@@ -4064,10 +4061,10 @@
         <v>82</v>
       </c>
       <c r="G83" t="s">
+        <v>88</v>
+      </c>
+      <c r="H83" t="s">
         <v>89</v>
-      </c>
-      <c r="H83" t="s">
-        <v>90</v>
       </c>
       <c r="I83">
         <v>100</v>
@@ -4082,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
@@ -4093,10 +4090,10 @@
         <v>15</v>
       </c>
       <c r="C84" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D84" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E84">
         <v>17</v>
@@ -4105,10 +4102,10 @@
         <v>83</v>
       </c>
       <c r="G84" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I84">
         <v>100</v>
@@ -4123,7 +4120,7 @@
         <v>1</v>
       </c>
       <c r="M84" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
@@ -4134,10 +4131,10 @@
         <v>15</v>
       </c>
       <c r="C85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D85" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E85">
         <v>18</v>
@@ -4146,10 +4143,10 @@
         <v>84</v>
       </c>
       <c r="G85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I85">
         <v>100</v>
@@ -4175,10 +4172,10 @@
         <v>15</v>
       </c>
       <c r="C86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D86" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E86">
         <v>18</v>
@@ -4187,10 +4184,10 @@
         <v>85</v>
       </c>
       <c r="G86" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I86">
         <v>100</v>
@@ -4216,10 +4213,10 @@
         <v>15</v>
       </c>
       <c r="C87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D87" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E87">
         <v>19</v>
@@ -4228,16 +4225,16 @@
         <v>86</v>
       </c>
       <c r="G87" t="s">
+        <v>76</v>
+      </c>
+      <c r="H87" t="s">
         <v>77</v>
-      </c>
-      <c r="H87" t="s">
-        <v>78</v>
       </c>
       <c r="I87">
         <v>-120</v>
       </c>
       <c r="J87" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K87">
         <v>0.5454545454545454</v>
@@ -4257,10 +4254,10 @@
         <v>15</v>
       </c>
       <c r="C88" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D88" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E88">
         <v>19</v>
@@ -4269,16 +4266,16 @@
         <v>87</v>
       </c>
       <c r="G88" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I88">
         <v>120</v>
       </c>
       <c r="J88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K88">
         <v>0.45454545454545453</v>
